--- a/PLANTILLA_ULIANOV_PORTICOS_2D_OFICIAL.xlsx
+++ b/PLANTILLA_ULIANOV_PORTICOS_2D_OFICIAL.xlsx
@@ -52040,6 +52040,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" algorithmName="SHA-512" hashValue="AyplFLVt1Bfxf3wSsFQue/pwQRAPVQrC2Bl8ee4kC5xE7YrrIn/1Vdj+Q3F8NaKfK477UFnmPioxNqMUjxmrDw==" saltValue="NIBvyInaIKNn0A7ZoE56vA==" spinCount="100000"/>
   <mergeCells count="11">
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="C7:D7"/>
@@ -58456,6 +58457,7 @@
       <c r="H148" s="56"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" algorithmName="SHA-512" hashValue="+++XiMroOHyA+j8SxiJt5lbtLwPhJdkYx4sbjqS0dcNLSjY00yJkIx6hCpRowu8aJGr9elUciGa4CVbwXGMIkA==" saltValue="Lj5P9f7qnyBQlQwYKH7rVg==" spinCount="100000"/>
   <mergeCells count="13">
     <mergeCell ref="B1:N1"/>
     <mergeCell ref="B2:N2"/>
